--- a/LivreCompta.xlsx
+++ b/LivreCompta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Journal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +417,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Libellé</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>DateValeur</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MontantDébit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MontantCrédit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CompteDébit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>CompteCrédit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Année</t>
         </is>
@@ -924,7 +912,11 @@
           <t>22/02/2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>factures</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>22/02/2026</t>
@@ -968,20 +960,14 @@
       <c r="E17" t="n">
         <v>87000000</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="F17" t="n">
+        <v>512</v>
+      </c>
+      <c r="G17" t="n">
+        <v>131</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2026</v>
       </c>
     </row>
   </sheetData>

--- a/LivreCompta.xlsx
+++ b/LivreCompta.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OCR_Imports" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,6 +971,685 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Facture - 01 - ANDRIANASOAVINA MANAMBIMANA VICTORIEN À  - DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>607</v>
+      </c>
+      <c r="G18" t="n">
+        <v>401</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Facture - 01 - ANDRIANASOAVINA MANAMBIMANA VICTORIEN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>701</v>
+      </c>
+      <c r="G19" t="n">
+        <v>411</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Facture - 02 - ANDRIANASOAVINA MANAMBIMANA VICTORIEN À  - DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>607</v>
+      </c>
+      <c r="G20" t="n">
+        <v>401</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>imported_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>invoice_number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>supplier_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>invoice_subject</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>date_valeur</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>type_operation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>libelle</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>montant_debit</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>montant_credit</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>montant_ht</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>montant_tva</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>montant_ttc</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>compte_debit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>compte_credit</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>annee</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>confidence_score</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>parse_warnings</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-05T16:06:12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>/home/andrianasoavina/Bureau/projet/TsaraKonta/EtatFiFolder/ocr_saved/Facture n°01_20260304_135051.json</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ANDRIANASOAVINA MANAMBIMANA VICTORIEN À L’ATTENTION DE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Facture - 01 - ANDRIANASOAVINA MANAMBIMANA VICTORIEN À  - DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>607</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>401</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Montant detecte sans mot-cle prioritaire</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>FACTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-05T16:06:12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>/home/andrianasoavina/Bureau/projet/TsaraKonta/EtatFiFolder/ocr_saved/Facture n°01_20260304_140555.json</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ANDRIANASOAVINA MANAMBIMANA VICTORIEN À L’ATTENTION DE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Facture - 01 - ANDRIANASOAVINA MANAMBIMANA VICTORIEN À  - DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>607</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>401</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Montant detecte sans mot-cle prioritaire</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>FACTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-05T16:06:12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>/home/andrianasoavina/Bureau/projet/TsaraKonta/EtatFiFolder/ocr_saved/Facture n°01_20260304_141626.json</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ANDRIANASOAVINA MANAMBIMANA VICTORIEN À L’ATTENTION DE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Facture - 01 - ANDRIANASOAVINA MANAMBIMANA VICTORIEN À  - DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>607</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>401</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Montant detecte sans mot-cle prioritaire</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>FACTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-05T16:06:12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>/home/andrianasoavina/Bureau/projet/TsaraKonta/EtatFiFolder/ocr_saved/Facture n°01_20260305_160201.json</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ANDRIANASOAVINA MANAMBIMANA VICTORIEN À L’ATTENTION DE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vente</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Facture - 01 - ANDRIANASOAVINA MANAMBIMANA VICTORIEN</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>701</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>411</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Montant detecte sans mot-cle prioritaire</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>FACTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-05T16:06:12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>/home/andrianasoavina/Bureau/projet/TsaraKonta/EtatFiFolder/ocr_saved/Facture n°02_20260304_135007.json</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ANDRIANASOAVINA MANAMBIMANA VICTORIEN À L’ATTENTION DE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Facture - 02 - ANDRIANASOAVINA MANAMBIMANA VICTORIEN</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>607</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>401</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Montant detecte sans mot-cle prioritaire</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>FACTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-05T16:06:12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>/home/andrianasoavina/Bureau/projet/TsaraKonta/EtatFiFolder/ocr_saved/Facture n°02_20260304_135918.json</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ANDRIANASOAVINA MANAMBIMANA VICTORIEN À L’ATTENTION DE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Facture - 02 - ANDRIANASOAVINA MANAMBIMANA VICTORIEN À  - DESCRIPTION PU QUANTITÉ TOTAL</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Montant detecte sans mot-cle prioritaire</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>FACTURE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
